--- a/src/src/main/resources/template/APM_AssetArrivalItem_Template.xlsx
+++ b/src/src/main/resources/template/APM_AssetArrivalItem_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503310146\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EC2059-6CA2-47BC-80CA-47220AAA5DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7B1988-B894-4D45-8A9C-6A301917F70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="4500" windowWidth="19410" windowHeight="8310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -24,129 +24,9 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
-  <si>
-    <t>到货单名称/编号</t>
-  </si>
-  <si>
-    <t>合同号</t>
-  </si>
-  <si>
-    <t>所属科室</t>
-  </si>
-  <si>
-    <t>经办人</t>
-  </si>
-  <si>
-    <t>到货日期</t>
-  </si>
-  <si>
-    <t>商务验收日期</t>
-  </si>
-  <si>
-    <t>设备型号</t>
-  </si>
-  <si>
-    <t>资产编号</t>
-  </si>
-  <si>
-    <t>当前状态</t>
-  </si>
-  <si>
-    <t>安装流程类型</t>
-  </si>
-  <si>
-    <t>制造商</t>
-  </si>
-  <si>
-    <t>供应商</t>
-  </si>
-  <si>
-    <t>制造商序列号</t>
-  </si>
-  <si>
-    <t>采购日期</t>
-  </si>
-  <si>
-    <t>当前处理人</t>
-  </si>
-  <si>
-    <t>安装工时</t>
-  </si>
-  <si>
-    <t>资产名称</t>
-  </si>
-  <si>
-    <t>创建人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所属院区</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备别名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备编号（院方）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二维码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出厂日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启用日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>维保截止日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>质保截止日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>维修负责人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>维修负责人2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>维修负责人3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安装位置编码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安装位置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,21 +36,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -197,12 +62,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -483,133 +344,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="13.125" customWidth="1"/>
-    <col min="6" max="6" width="11.375" customWidth="1"/>
-    <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="13" max="13" width="13.125" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="19" max="19" width="11.75" customWidth="1"/>
-    <col min="22" max="22" width="17.5" customWidth="1"/>
-    <col min="26" max="26" width="13.875" customWidth="1"/>
-    <col min="27" max="27" width="13.75" customWidth="1"/>
-    <col min="28" max="28" width="13.125" customWidth="1"/>
-    <col min="29" max="29" width="15.25" customWidth="1"/>
-    <col min="30" max="30" width="16.5" customWidth="1"/>
-    <col min="31" max="31" width="14.25" customWidth="1"/>
-    <col min="32" max="32" width="17.875" customWidth="1"/>
-    <col min="33" max="33" width="10.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:34" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="163" orientation="portrait" r:id="rId1"/>
